--- a/templates/template_pape.xlsx
+++ b/templates/template_pape.xlsx
@@ -835,42 +835,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>447675</colOff>
-      <row>0</row>
-      <rowOff>104775</rowOff>
-    </from>
-    <ext cx="1095375" cy="1095375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="image1.png"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_1" displayName="Table_1" ref="A1:A31" headerRowCount="1">
   <tableColumns count="1">
@@ -29185,7 +29149,6 @@
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" scale="45"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
